--- a/results/Int Task Remove ACC 0.4/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.278675068833498e-05</v>
+        <v>-0.00238910544623132</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.007544775245605909</v>
+        <v>-0.006902064874414823</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0001426843364834739</v>
+        <v>-0.001375887274962607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00040156633998623</v>
+        <v>0.002498085150721739</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.002673967794926081</v>
+        <v>-0.003379234982350435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008179804390217264</v>
+        <v>-0.0005577912061493273</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.952154885711324e-05</v>
+        <v>0.0001094373811768323</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006140968869010599</v>
+        <v>0.001439172860390141</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01139387556415993</v>
+        <v>0.01071903285177538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01245896193955258</v>
+        <v>0.01203125488718245</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001168502184302578</v>
+        <v>0.001891318464897796</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.001988560417715185</v>
+        <v>-0.003282715484117872</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0007019699415035253</v>
+        <v>-0.002292735727560182</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001661690713642887</v>
+        <v>8.187188158309093e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00793071635655399</v>
+        <v>0.00898588982316763</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001617232304260854</v>
+        <v>0.0006537937257478067</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.000651573036517059</v>
+        <v>-0.001479879935369846</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005848187204112242</v>
+        <v>-0.0007567341511143076</v>
       </c>
       <c r="U3" t="n">
-        <v>0.000416753325977498</v>
+        <v>-0.00189398846352479</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000136894413087737</v>
+        <v>0.0001724291516358156</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001240200638466108</v>
+        <v>0.0002787363755470142</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002700724362832242</v>
+        <v>0.0004301678183084977</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007943863007475515</v>
+        <v>-0.0002326883485704457</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0007321353329560165</v>
+        <v>0.001263065991257597</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001289659207563819</v>
+        <v>-0.001127157087619854</v>
       </c>
       <c r="AB3" t="n">
-        <v>-8.484561744427245e-05</v>
+        <v>0.0002144278563029101</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.00188478525709915</v>
+        <v>-0.002276544374808632</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0005566208877427429</v>
+        <v>-0.0004440215546212233</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.0008163115595313131</v>
+        <v>0.0004289811922637277</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001501142036102189</v>
+        <v>0.0028712106648475</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0005924190129154438</v>
+        <v>9.493960029161586e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0002068193593753853</v>
+        <v>4.254759220753466e-05</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0006662626451489951</v>
+        <v>0.003111178832939528</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.001221346507197776</v>
+        <v>-0.001839989993859128</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0002027181535013822</v>
+        <v>0.0002224542986187483</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0005196181910993958</v>
+        <v>0.0008330885387928987</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001092685836006388</v>
+        <v>-0.0005881634928336188</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0007144345315986467</v>
+        <v>0.0008531934427861296</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0006165339179322471</v>
+        <v>0.0001758110714399574</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2.025540615481877e-05</v>
+        <v>-0.0006281136351439563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00133224872250539</v>
+        <v>-0.0001668870716744308</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.001138651034570187</v>
+        <v>-0.0004898094720743108</v>
       </c>
       <c r="AT3" t="n">
-        <v>-4.733822363797574e-05</v>
+        <v>-0.0012061181214258</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.00564479994981035</v>
+        <v>-0.005657778711320882</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.001420798140170178</v>
+        <v>0.0008789828880393548</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0009819618571408029</v>
+        <v>0.002095789982490089</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0001637176234786619</v>
+        <v>-0.0001823041193733677</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001661293442150749</v>
+        <v>0.00251697626734857</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0006974837852776162</v>
+        <v>0.00190125003173195</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.003786142855572572</v>
+        <v>-0.005013900239538597</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.00355311462097808</v>
+        <v>0.0005099162011794978</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0001450209965870342</v>
+        <v>0.0001081047442502946</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.000289591506991802</v>
+        <v>-0.0001923231042853047</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0001677595511229302</v>
+        <v>-0.0005309166310473513</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.005775338499428968</v>
+        <v>-0.0007549064877655145</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0001731627130372395</v>
+        <v>0.00180602593327139</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0.0005416168068038251</v>
+        <v>-0.00017267576290246</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.002864954524340462</v>
+        <v>0.002953036901376163</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002416972493200166</v>
+        <v>-0.0007703561357852183</v>
       </c>
       <c r="BL3" t="n">
-        <v>-8.328313656070008e-05</v>
+        <v>-0.0002096713087646496</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0006883235070625127</v>
+        <v>-0.0008057665349042165</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.0021791408135094</v>
+        <v>-0.002082504440484695</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001758738160857583</v>
+        <v>-0.001195941572083106</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001129571642887381</v>
+        <v>-0.0003229088588566329</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.038937870345376e-05</v>
+        <v>0.0001672966314901902</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0007639736326025393</v>
+        <v>-0.001104677935127326</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0007434760163340983</v>
+        <v>0.0008617419961537032</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0001205692107050127</v>
+        <v>0.0003422806413234636</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.001622498924275228</v>
+        <v>-0.002524610211037943</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.001619788330304313</v>
+        <v>0.001986718490405084</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.002085158662182451</v>
+        <v>0.001905832271381032</v>
       </c>
       <c r="BX3" t="n">
-        <v>-2.189880794106203e-05</v>
+        <v>-0.0001064097944895937</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.738645190434097e-05</v>
+        <v>-9.995366874393728e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0001587678606220677</v>
+        <v>1.251161345571461e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.798561151078903e-05</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0002763048650130662</v>
+        <v>-0.000201518812279673</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.000261761361257402</v>
+        <v>5.749079167439944e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0001487210827136032</v>
+        <v>0.0001214789706750696</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0001761032892737013</v>
+        <v>0.0002068622523375174</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0002578960759141113</v>
+        <v>0.00110833549538374</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0006538914226997561</v>
+        <v>-0.0009006923265258025</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.000123959979082161</v>
+        <v>0.0005652275755540537</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0009393365196961901</v>
+        <v>0.001177263496568105</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0.002335905982769865</v>
+        <v>0.001808533697822531</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0001386967224275959</v>
+        <v>0.0007051838211678996</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006454000152243016</v>
+        <v>0.007381976621820216</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01153679794542705</v>
+        <v>0.01230434211018825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004866575810181828</v>
+        <v>0.008185866379668821</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006584165100733803</v>
+        <v>0.005952393320816846</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00571552583024126</v>
+        <v>0.00757920748308622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005197324016080272</v>
+        <v>0.00661478904054377</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002675424407229405</v>
+        <v>0.0002876126822140468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004848901123575121</v>
+        <v>0.005383429222660986</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02460340551619081</v>
+        <v>0.01435050761892957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02150570304404763</v>
+        <v>0.01540770646736553</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004023370841461451</v>
+        <v>0.005330650922318558</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004147541881642972</v>
+        <v>0.01201056592468413</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005246540417849717</v>
+        <v>0.007942906665985237</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02201170941168382</v>
+        <v>0.01767737469125163</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01564400159682664</v>
+        <v>0.008376148856672427</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004887686327844982</v>
+        <v>0.003199381276710463</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003768766659071218</v>
+        <v>0.005388890271094601</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005784863554867892</v>
+        <v>0.004846899997334863</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004727839902902561</v>
+        <v>0.006297315353542108</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0003933846261175078</v>
+        <v>0.0003719085327453049</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005556915066002745</v>
+        <v>0.005736832952181797</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004643594068825314</v>
+        <v>0.005084414828302289</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003267504116656435</v>
+        <v>0.002531001794567863</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003097032319969771</v>
+        <v>0.001410976968798014</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002750135735064335</v>
+        <v>0.002037903594203356</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007502439677880396</v>
+        <v>0.0005690588893232726</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.007063917895132196</v>
+        <v>0.008713444408228476</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01194637004059061</v>
+        <v>0.01188447207683726</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005249040126728638</v>
+        <v>0.00654914950885997</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005410892041881041</v>
+        <v>0.005697923982710675</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006485609977588395</v>
+        <v>0.0004589046932541437</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001049618341726122</v>
+        <v>0.0008229594873231727</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.003175664786282348</v>
+        <v>0.005279216554075934</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.007183335535529779</v>
+        <v>0.009231716170629756</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0003292399825253022</v>
+        <v>0.0008969279385940929</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0009637099404637278</v>
+        <v>0.001311940232532011</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002272556441449447</v>
+        <v>0.003910343010192107</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003849153443924003</v>
+        <v>0.004939921326159356</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001467012489417014</v>
+        <v>0.00121164468825907</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001476028126701482</v>
+        <v>0.002967384431664734</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004861421174444756</v>
+        <v>0.005095534942677467</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003015373233336913</v>
+        <v>0.002279387937104924</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01156111920612921</v>
+        <v>0.009683008582612508</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.006360428600967376</v>
+        <v>0.006860983164031498</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001577021002870566</v>
+        <v>0.001988862825173743</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.005202244376203913</v>
+        <v>0.003052745376026381</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005474763856394547</v>
+        <v>0.0004202830344564702</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002641867629214904</v>
+        <v>0.003900251004639385</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00903009003720313</v>
+        <v>0.009522921126050398</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008612779378374373</v>
+        <v>0.009406523235077987</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005614442743853709</v>
+        <v>0.007286322647827714</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.000874583635716496</v>
+        <v>0.001357396507247332</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005041113177118624</v>
+        <v>0.001453959985009074</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.00174212817899834</v>
+        <v>0.001858827414619011</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.007056555730639066</v>
+        <v>0.007194607350946818</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.008351598790374908</v>
+        <v>0.007030526560069183</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001166225936414071</v>
+        <v>0.0008830426442533901</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002506303030023022</v>
+        <v>0.005567970021772806</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.009225386428470565</v>
+        <v>0.006711835845276418</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0006570913834608172</v>
+        <v>0.002648789186185431</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002064245567867679</v>
+        <v>0.00469957791948305</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.009353076263198451</v>
+        <v>0.007771927937651554</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.005424522722558353</v>
+        <v>0.006819679092569903</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002828703114385706</v>
+        <v>0.004935538097184456</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002861177420970779</v>
+        <v>0.0001730834942581494</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.006293188172056757</v>
+        <v>0.005112111062999113</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.005799462203035569</v>
+        <v>0.001495106366711996</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002750732780826753</v>
+        <v>0.00138029696817059</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.006628486513798647</v>
+        <v>0.004537868717508334</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.005154692040555789</v>
+        <v>0.002274149196997115</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.009913912644726033</v>
+        <v>0.006805793286440469</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001927742475512022</v>
+        <v>0.000169525753795223</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0006043537053037657</v>
+        <v>0.0006657138745160712</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0006522718099635361</v>
+        <v>0.0006566890129030868</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.687549748503541e-05</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001973318824763591</v>
+        <v>0.0009984998632322981</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.003151070403581045</v>
+        <v>0.002680283650571455</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0004020554266713833</v>
+        <v>0.0004319651039365459</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001187088723063805</v>
+        <v>0.0009292309728990236</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003727403457924915</v>
+        <v>0.002015957143433268</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002690770537621391</v>
+        <v>0.002873511227779463</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009449420873003612</v>
+        <v>0.001289369963942071</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003012223413540237</v>
+        <v>0.00350219866600978</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004262834417654134</v>
+        <v>0.004881489549077966</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002115997464353479</v>
+        <v>0.00278142916130043</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.009982014388489235</v>
+        <v>-0.01803057553956833</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02727663230240542</v>
+        <v>-0.03313848920863309</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.009288354898336371</v>
+        <v>-0.01812050359712226</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.007948243992606241</v>
+        <v>-0.005961182994454683</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01173561151079138</v>
+        <v>-0.02221223021582732</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.006579561362575826</v>
+        <v>-0.01016187050359712</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000430292598967319</v>
+        <v>-0.0003865979381443285</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.007466168922071859</v>
+        <v>-0.007279514699020062</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01987867475501632</v>
+        <v>-0.008586094260382638</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.007699486700886604</v>
+        <v>-0.0119415807560137</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005075187969924844</v>
+        <v>-0.003049907578558198</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01072088724584098</v>
+        <v>-0.03453237410071939</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01128597122302161</v>
+        <v>-0.0144639556377079</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03825187969924813</v>
+        <v>-0.03637218045112781</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02235184321045263</v>
+        <v>-0.002006532897806812</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00365120274914088</v>
+        <v>-0.004806346243583759</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00732913669064752</v>
+        <v>-0.01115107913669063</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01024096385542168</v>
+        <v>-0.0110161870503597</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006958762886597913</v>
+        <v>-0.01758093525179854</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0005132991133924402</v>
+        <v>-0.0004344048653345256</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.009986000933271112</v>
+        <v>-0.009799346710219314</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.00678694158075599</v>
+        <v>-0.008897403150276696</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.002777777777777801</v>
+        <v>-0.004293047130191319</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.007583774250440945</v>
+        <v>-0.0008399440037330841</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.006084656084656115</v>
+        <v>-0.003605560382276318</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001663585951940771</v>
+        <v>-0.0005154639175257714</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01843033509700177</v>
+        <v>-0.01686151079136688</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02989690721649481</v>
+        <v>-0.02787800687285225</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01361683848797246</v>
+        <v>-0.01258591065292092</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.005086327578161453</v>
+        <v>-0.007364836100468253</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001913205786280914</v>
+        <v>-0.0006066262249183385</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001571164510166301</v>
+        <v>-0.0009332711152589823</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.006271477663230218</v>
+        <v>-0.003522336769759438</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01752577319587623</v>
+        <v>-0.02452749140893471</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0006744604316546998</v>
+        <v>-0.001386321626617315</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001617375231053564</v>
+        <v>-0.001432532347504567</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.005467372134038817</v>
+        <v>-0.005739617358842741</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005599647266313945</v>
+        <v>-0.008204467353951861</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.004037800687285209</v>
+        <v>-0.001315789473684192</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002443609022556403</v>
+        <v>-0.005360443622920485</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.0101374570446735</v>
+        <v>-0.007705406555981243</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.005412972468502098</v>
+        <v>-0.00317312179188054</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01696735395188997</v>
+        <v>-0.02156357388316149</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.01332481907194554</v>
+        <v>-0.01816546762589926</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.0007054673721340499</v>
+        <v>-0.001973684210526305</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01390573961735884</v>
+        <v>-0.00317869415807559</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001455026455026487</v>
+        <v>-0.000944244604316491</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.003865979381443285</v>
+        <v>-0.002171903881700499</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.009658040665434331</v>
+        <v>-0.02171903881700552</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01651889874008399</v>
+        <v>-0.02109106529209619</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01385907606159589</v>
+        <v>-0.007699486700886604</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001879699248120303</v>
+        <v>-0.001524953789279071</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001293900184842811</v>
+        <v>-0.002620274914089338</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.004699248120300803</v>
+        <v>-0.004297597042513835</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02088724584103507</v>
+        <v>-0.00993530499075781</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01293900184842878</v>
+        <v>-0.007326178254783012</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003007518796992503</v>
+        <v>-0.002108433734939785</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001532567049808442</v>
+        <v>-0.005283505154639156</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01945471349353045</v>
+        <v>-0.01390942698706095</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0009036144578313254</v>
+        <v>-0.007087628865979356</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003406439570695286</v>
+        <v>-0.007388316151202723</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01048109965635735</v>
+        <v>-0.01752577319587624</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.01059262715818945</v>
+        <v>-0.01249999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.005908289241622599</v>
+        <v>-0.01000425713069387</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0003696857670979048</v>
+        <v>-4.295532646048095e-05</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01009700176366846</v>
+        <v>-0.01039518900343639</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.008820998278829605</v>
+        <v>-0.001080827067669177</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004343807763401064</v>
+        <v>-0.001268796992481214</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.01552680221811456</v>
+        <v>-0.0141404805914972</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.01009700176366847</v>
+        <v>-0.0009398496240601406</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.02592421441774488</v>
+        <v>-0.01275415896487983</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0004295532646048095</v>
+        <v>-0.0004046762589927533</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0007495590828924259</v>
+        <v>-0.001119925338310779</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001106853980417244</v>
+        <v>-0.0007988721804511268</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.005314232902033211</v>
+        <v>-0.002554278416347366</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.005291005291005302</v>
+        <v>-0.004573028464769013</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0001399906672888474</v>
+        <v>-0.0001702852277564837</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002911275415896431</v>
+        <v>-0.0008866075594960332</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.004819277108433728</v>
+        <v>-0.00315027671349507</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.004518072289156627</v>
+        <v>-0.004339710685954267</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.00124768946395557</v>
+        <v>-0.001034172661870469</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.005952380952380975</v>
+        <v>-0.003079794680354642</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.009286047596826875</v>
+        <v>-0.004384844614729644</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.003615520282186968</v>
+        <v>-0.002724563644103839</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002111454631094803</v>
+        <v>-0.006492277662588797</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01689808867191963</v>
+        <v>-0.007921138590760612</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001823708558926052</v>
+        <v>-0.00501491187660002</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.002224028176110379</v>
+        <v>-0.0002744189906239925</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.006495197469291525</v>
+        <v>-0.003317882119785781</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.002288617856902808</v>
+        <v>-0.005079806798178821</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0002858359180198278</v>
+        <v>-5.807507413661539e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001102200153999472</v>
+        <v>-0.00283248496987849</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003247895854404353</v>
+        <v>-0.0007527305613252572</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.00190366705726937</v>
+        <v>0.003768082127858141</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003348581982084728</v>
+        <v>-0.002301492139621603</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.00327433139623452</v>
+        <v>-0.004096441321656773</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.003155818392175913</v>
+        <v>-0.00860817789067712</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.008337058293909688</v>
+        <v>-0.008823852561635906</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.003827490297336647</v>
+        <v>0.001927453299433712</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.002330518343141641</v>
+        <v>-0.001631232636831609</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.003257508736365364</v>
+        <v>-0.00509588517392014</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001443833069692177</v>
+        <v>-0.00317312179188054</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002157578596505658</v>
+        <v>-0.002193187120858609</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.227194492255725e-05</v>
+        <v>-3.499766682221183e-05</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003578626886721614</v>
+        <v>-0.003044964937020009</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003188996421910106</v>
+        <v>-0.002383963876092479</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001023038549762781</v>
+        <v>-0.001889185725429995</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0005369498427939185</v>
+        <v>0.0006399938377849773</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.00207129263671578</v>
+        <v>-0.003112296394868869</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0003371110600658894</v>
+        <v>-0.0002662693212250433</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002400919255985348</v>
+        <v>-0.007832610542013289</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.001815737637848872</v>
+        <v>-0.004631672108045398</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.001843426301700368</v>
+        <v>-0.0002456495711985612</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001306406981694372</v>
+        <v>0.001523096152103051</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0007695628137963761</v>
+        <v>-0.0002574439441218656</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0003370890642199032</v>
+        <v>-0.0005967663361904131</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.002983345348993199</v>
+        <v>4.824682544762903e-06</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.004619621971595686</v>
+        <v>-0.004396833314560633</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0004291477165732888</v>
+        <v>-0.0002699236796811499</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001133484836022927</v>
+        <v>0.000119127302862207</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0021263095688802</v>
+        <v>-0.003816717122129531</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.004416238210600684</v>
+        <v>-0.002080175895826972</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0006326395355301439</v>
+        <v>-0.000302198717216709</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0006526734128377675</v>
+        <v>-0.002602074966532836</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0008732769423559022</v>
+        <v>-0.004377668681737007</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.003768525920484514</v>
+        <v>-0.002443507632137232</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.00807112936155455</v>
+        <v>-0.001612401988908063</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.01064888168830017</v>
+        <v>-0.007549442021178856</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.0002445978114631986</v>
+        <v>-0.0003077670144581935</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0015757281010125</v>
+        <v>0.001100448047764199</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003307290464540397</v>
+        <v>-0.0005398379143144949</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0002981074657877503</v>
+        <v>-1.976524965030535e-05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.005167732793717361</v>
+        <v>0.0004344048653344812</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006570242679111124</v>
+        <v>-0.008876550765920149</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.007151645928843397</v>
+        <v>-0.006742634243120946</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0004979989285854858</v>
+        <v>-0.0007588239821812559</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0004494073247350516</v>
+        <v>-0.0007918572720381546</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0003082618743538185</v>
+        <v>-0.0003599437872526701</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.008845221722060639</v>
+        <v>-0.006240403703899689</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.007464550330092534</v>
+        <v>-0.002914049423023488</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.00100728446640728</v>
+        <v>-0.0002333177788147456</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.001544620920854273</v>
+        <v>0.0002227208975541933</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.004938670024011385</v>
+        <v>-0.004601164429281301</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005574465956514118</v>
+        <v>-0.0007701953641687047</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.00226057367989782</v>
+        <v>-0.005242352368789149</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.007766091163854616</v>
+        <v>-0.006414818549488491</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.005086130876360786</v>
+        <v>-0.005700678950423608</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.002005832689078261</v>
+        <v>-0.001518127958136126</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-6.999533364442366e-05</v>
+        <v>1.155268022181299e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001249944882841353</v>
+        <v>-0.004644161276494064</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001964070481023805</v>
+        <v>-8.700226308518133e-05</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.001261464441889437</v>
+        <v>-0.0006298124301753444</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.004492310954370101</v>
+        <v>-0.003566160814095851</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.005632399420794609</v>
+        <v>0.0006895897337142853</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.004501474593051824</v>
+        <v>-0.0009574112471901402</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>-0.000209290587580091</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.000465829790322117</v>
+        <v>-0.0006349039789099953</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006892487946092208</v>
+        <v>-0.0004587864319895857</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003128465972108557</v>
+        <v>-0.0003656054349870624</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001438311920076909</v>
+        <v>-0.001825889518640808</v>
       </c>
       <c r="CD6" t="n">
-        <v>-3.227194492254893e-05</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0006674288976733333</v>
+        <v>-0.0005722041776162313</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002018243483640053</v>
+        <v>0.0001886158695708323</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001748602562298338</v>
+        <v>-0.003053784984140418</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0007182349358608481</v>
+        <v>-0.0001214150106418038</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.00275571506024899</v>
+        <v>-0.001094448356463174</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.004032797858099071</v>
+        <v>-0.001151279315233614</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.002017681197330834</v>
+        <v>-0.001108106249000001</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.001026491854307748</v>
+        <v>0.0006962493970376682</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.005086327578161454</v>
+        <v>-0.00365497076023395</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004811510508352822</v>
+        <v>0.001693021212825879</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0002689118546432945</v>
+        <v>0.0006732771677395056</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.002016496658836658</v>
+        <v>-0.001123707980871452</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0006191432396251584</v>
+        <v>-0.001611537301022037</v>
       </c>
       <c r="I7" t="n">
-        <v>2.333177788147456e-05</v>
+        <v>0.0001790899381381272</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0003205065171049237</v>
+        <v>0.002291206940099139</v>
       </c>
       <c r="K7" t="n">
-        <v>0.005260526955663691</v>
+        <v>0.01161760371492174</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008742495728888638</v>
+        <v>0.01149436478124785</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.536486846654089e-05</v>
+        <v>-0.000903605280839237</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001366953062733484</v>
+        <v>-0.0008410952427732876</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001218603661132411</v>
+        <v>-0.001731091367789095</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002652902560529119</v>
+        <v>-0.002008468277977271</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01169637499093252</v>
+        <v>0.01092463657939631</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0005634163862759888</v>
+        <v>0.001100895491748505</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008841547835415187</v>
+        <v>0.0007763627161698039</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0005187858579212112</v>
+        <v>-0.0002953916097908959</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00074116544840786</v>
+        <v>-0.0009860524109842673</v>
       </c>
       <c r="V7" t="n">
-        <v>2.333177788147456e-05</v>
+        <v>0.0001290877796901901</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001329514022792866</v>
+        <v>0.002339247342358225</v>
       </c>
       <c r="X7" t="n">
-        <v>7.82184696458744e-05</v>
+        <v>0.002395918503695288</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0002496162980888006</v>
+        <v>0.0003196591064977717</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.494331249622839e-05</v>
+        <v>0.001279003307714782</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001362230783300566</v>
+        <v>-0.00107326178254783</v>
       </c>
       <c r="AB7" t="n">
-        <v>-2.186168275160049e-05</v>
+        <v>0.0001987052586299998</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0001914888268960524</v>
+        <v>-0.001973065418894643</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005896837314973851</v>
+        <v>0.0006502843702050122</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0003541840712892929</v>
+        <v>0.003291207156668979</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.628682143411276e-05</v>
+        <v>0.003610420333437481</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0004713613975470765</v>
+        <v>0.0002048315137169632</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0001763668430335041</v>
+        <v>-0.0001643092214904995</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0004071696432133565</v>
+        <v>0.001734939161950605</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001189402883823187</v>
+        <v>0.0008892654822537816</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0001864278056139257</v>
+        <v>0.0001620365226680354</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0007462195864961496</v>
+        <v>0.0004746918113936238</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0009324994026744138</v>
+        <v>-0.0003219947933920553</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.000430036320166194</v>
+        <v>0.0008605709417428609</v>
       </c>
       <c r="AP7" t="n">
-        <v>-7.204145805633776e-05</v>
+        <v>2.473305765702815e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0003393015787581</v>
+        <v>-0.0008666367816831833</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.002512877821666926</v>
+        <v>-0.0002850799155355965</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0003296125046096943</v>
+        <v>-0.0006556841497101618</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0008329614755317738</v>
+        <v>-0.0003727961302038896</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.006829718705265925</v>
+        <v>-0.005533684585636699</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001172351376525582</v>
+        <v>0.0001061992908690024</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0007636365568092552</v>
+        <v>0.001694588673512276</v>
       </c>
       <c r="AX7" t="n">
-        <v>-6.931608133084466e-05</v>
+        <v>4.257130693912648e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.00228842489047823</v>
+        <v>0.001196508041177824</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.002147281162951081</v>
+        <v>0.002537086871855915</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.004656896871809174</v>
+        <v>-0.003099061726137526</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.002300451515386415</v>
+        <v>0.001123718459622902</v>
       </c>
       <c r="BC7" t="n">
-        <v>-4.883091640117682e-06</v>
+        <v>8.718873829015593e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.000198202642621903</v>
+        <v>-0.0004951276340613541</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0001633224451703219</v>
+        <v>-2.095847214496072e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.005339205646976692</v>
+        <v>-0.001535538486504023</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.003136200384994903</v>
+        <v>0.001728806904226982</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.0005130286322553024</v>
+        <v>-4.699248120298982e-05</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.002669525978969806</v>
+        <v>0.002345284418756655</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.002323756953373385</v>
+        <v>0.001004552371405665</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.000176916989152337</v>
+        <v>0.0003635944681711855</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0009362848218269937</v>
+        <v>0.001221238336805858</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.0055442635202464</v>
+        <v>-0.001596590347792082</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.001500655145986318</v>
+        <v>0.0003193762986081983</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0004936622786237521</v>
+        <v>0.0005229683210809244</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.349624060148936e-05</v>
+        <v>0.0001571840719345796</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0009720100606971538</v>
+        <v>-0.0003981203884653228</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.000397722626051733</v>
+        <v>0.000440360353055963</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0005772148745357364</v>
+        <v>0.0001551933056729238</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.002099718113203097</v>
+        <v>-0.001358720876264757</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.001565152038004231</v>
+        <v>0.001177580235189984</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0008194080920920998</v>
+        <v>0.001892255836289142</v>
       </c>
       <c r="BX7" t="n">
-        <v>2.220446049250313e-17</v>
+        <v>-6.814121899318959e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.458085656321777e-05</v>
+        <v>1.303769391480808e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-6.999533364442368e-05</v>
+        <v>2.310536044362599e-05</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-9.332711152589823e-05</v>
+        <v>5.551115123125783e-18</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0002999788056092135</v>
+        <v>0.0002645143787303239</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002661020019929294</v>
+        <v>0.0001303214596003244</v>
       </c>
       <c r="CF7" t="n">
-        <v>4.424721597807708e-05</v>
+        <v>0.00161836881356136</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.001076016598001473</v>
+        <v>-0.00132871942211088</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0002809681108978779</v>
+        <v>0.0003031864299302467</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.001268328098846044</v>
+        <v>0.0001219023772714156</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0.002368198993652726</v>
+        <v>0.0006963946009602206</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0006771149467228343</v>
+        <v>0.00032222835410049</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002469125515089099</v>
+        <v>0.001816287707219844</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002061034700130001</v>
+        <v>-0.0005709060134134664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00244075158770867</v>
+        <v>0.003059822800113335</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001740214133422094</v>
+        <v>0.003102116172272523</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0003364782066891309</v>
+        <v>0.0005818202685384466</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004028268952356554</v>
+        <v>0.003382250947280036</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001420695799011079</v>
+        <v>0.0003350959730256647</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001818177073379928</v>
+        <v>0.004226293983001209</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02412469251833286</v>
+        <v>0.01575136524935718</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01641763552399515</v>
+        <v>0.01482318161535025</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003656281324147009</v>
+        <v>0.005865652631626144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000591352120110622</v>
+        <v>0.00215116863970434</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003827628799355176</v>
+        <v>0.004110915631940331</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008348301471259926</v>
+        <v>0.01449345249411355</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01654967499705059</v>
+        <v>0.01528562569512909</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00617155710245261</v>
+        <v>0.003357131533653385</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001712614870509579</v>
+        <v>0.002077689431355495</v>
       </c>
       <c r="T8" t="n">
-        <v>0.002590571287706217</v>
+        <v>0.002308202852492044</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004570202520854716</v>
+        <v>0.001427179058757963</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002491763474761377</v>
+        <v>0.0002761235670708351</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00313437517045764</v>
+        <v>0.005010108454589731</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003581260609194639</v>
+        <v>0.004037902686012643</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00155365286644121</v>
+        <v>0.001640482198306106</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0009814148355021866</v>
+        <v>0.001884544627480472</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.0004588332427322706</v>
+        <v>0.0005651258706271423</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0003515527288044911</v>
+        <v>0.0005867140852937213</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001532868779432361</v>
+        <v>0.004430664484151598</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007741419646237877</v>
+        <v>0.006428506228259795</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.001743713630312108</v>
+        <v>0.003867538682880201</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003812535519946667</v>
+        <v>0.005293840270780042</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.000253382298338456</v>
+        <v>0.0004812483014765751</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008787445923697596</v>
+        <v>0.00039153082399416</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001541312908456707</v>
+        <v>0.00573709363482341</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.003374544473039251</v>
+        <v>0.003286431123889985</v>
       </c>
       <c r="AL8" t="n">
-        <v>9.920634920634609e-05</v>
+        <v>0.0004937572930161809</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.756588636538721e-05</v>
+        <v>0.001634693178728136</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.000869720889954692</v>
+        <v>0.00131569944977388</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.002596633966492909</v>
+        <v>0.003639653885816605</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001121919924377823</v>
+        <v>0.0002486963230743877</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0007911439726885878</v>
+        <v>0.0007287722914692263</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004780592096061265</v>
+        <v>0.004128707860223538</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.0002164743630607174</v>
+        <v>0.001548356839485382</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.005155627886917233</v>
+        <v>0.005527832167303976</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.001354250352382003</v>
+        <v>-0.002231537283931473</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.002363291443046612</v>
+        <v>0.002684513028867627</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007538598342075792</v>
+        <v>0.003278908827824981</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.60988786314587e-05</v>
+        <v>9.171557691113884e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003586937405927321</v>
+        <v>0.00553357846319017</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003108373022045427</v>
+        <v>0.007784467554582508</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001398466494617745</v>
+        <v>0.0008275164148657616</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0006596425859535488</v>
+        <v>0.005912392277313249</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002292889422778749</v>
+        <v>0.0004982335356463392</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.0001293961996677334</v>
+        <v>0.0002393572657310966</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0008809700487321437</v>
+        <v>0.0003795228912449988</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0008379812831754985</v>
+        <v>0.004119918828754135</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.003986705741329852</v>
+        <v>0.004068980721279578</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0004311850559315849</v>
+        <v>0.0001622499398046678</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004595837401213987</v>
+        <v>0.005546634121274416</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.003252818948712752</v>
+        <v>0.003693482457229086</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001577549862802841</v>
+        <v>0.001361054013931681</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001116560372951689</v>
+        <v>0.001514635235348824</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001906206288390161</v>
+        <v>0.00430496767999134</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0003220117311350468</v>
+        <v>0.003450128482708814</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002256699073778512</v>
+        <v>0.003052157766504823</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0001720431061506767</v>
+        <v>0.0002519611142389633</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.003153969288645386</v>
+        <v>0.003013769944699521</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004076344187807646</v>
+        <v>0.001607077075000932</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0002877357623230658</v>
+        <v>0.0007909019080089702</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.003682993454860148</v>
+        <v>0.0004666355576294912</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.00206584911883067</v>
+        <v>0.003668302119353481</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.004496598203626495</v>
+        <v>0.005398682345001802</v>
       </c>
       <c r="BX8" t="n">
-        <v>7.540401147846099e-05</v>
+        <v>-2.775557561562892e-18</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0003915444354313541</v>
+        <v>0.0001859414723860059</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0003460512271069638</v>
+        <v>0.0002472357071842401</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>5.962860017112159e-05</v>
+        <v>0.000178983797089341</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002941872148282482</v>
+        <v>0.001769914908676867</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0005493555178611553</v>
+        <v>0.0008466405303754422</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0009478216322381494</v>
+        <v>0.002290055389235821</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0004053210081581271</v>
+        <v>0.001369947185513712</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0003264204889559669</v>
+        <v>0.001375261981389098</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0001021550778746466</v>
+        <v>0.002794440164636311</v>
       </c>
       <c r="CJ8" t="n">
-        <v>9.100483368714709e-05</v>
+        <v>0.0055602740030198</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001432451563756168</v>
+        <v>0.0009739427459222044</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01534195933456565</v>
+        <v>0.005643738977072266</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005507745266781416</v>
+        <v>0.009466437177280528</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00634398496240598</v>
+        <v>0.007099827882960386</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01651766709237969</v>
+        <v>0.01394148020654042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007347504621072143</v>
+        <v>0.00434227330779059</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01021256931608138</v>
+        <v>0.0125661375661375</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0003006872852233666</v>
+        <v>0.0004733218588640176</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009964726631393283</v>
+        <v>0.009796672828096153</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06564748201438846</v>
+        <v>0.03866906474820144</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06582733812949638</v>
+        <v>0.04316546762589929</v>
       </c>
       <c r="M9" t="n">
-        <v>0.006081668114682881</v>
+        <v>0.01203919738684087</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003399311531841654</v>
+        <v>0.008421516754850023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005599626691553894</v>
+        <v>0.00996472663139324</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04604316546762587</v>
+        <v>0.02153776978417268</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03120300751879697</v>
+        <v>0.02117039586919102</v>
       </c>
       <c r="R9" t="n">
-        <v>0.008641975308641947</v>
+        <v>0.004276895943562564</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003604436229205232</v>
+        <v>0.003618561089825478</v>
       </c>
       <c r="T9" t="n">
-        <v>0.008133086876155304</v>
+        <v>0.005291005291005224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006261022927689574</v>
+        <v>0.004821894005212823</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0008377425044091447</v>
+        <v>0.0008093525179856287</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01212406015037592</v>
+        <v>0.005994787141615931</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007466168922071859</v>
+        <v>0.005845323741007202</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008273381294964011</v>
+        <v>0.00293742017879951</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002922661870503551</v>
+        <v>0.003448275862068984</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004046762589928032</v>
+        <v>0.002108433734939741</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009442446043165132</v>
+        <v>0.001234567901234529</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00723684210526312</v>
+        <v>0.0104526364909006</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.008605851979345958</v>
+        <v>0.01346815834767639</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.006019598693420436</v>
+        <v>0.007553956834532393</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01151079136690645</v>
+        <v>0.01049382716049377</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0003405704555129674</v>
+        <v>0.0006516072980016884</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002061855670103119</v>
+        <v>0.00159208261617898</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002736750651607312</v>
+        <v>0.01419965576592078</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.006238447319778228</v>
+        <v>0.008950086058519758</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0002147766323024047</v>
+        <v>0.0018041237113402</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001476976542137287</v>
+        <v>0.002913533834586479</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001633224451703219</v>
+        <v>0.007186187587494164</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.00489833641404811</v>
+        <v>0.009079173838209952</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0009122502172024593</v>
+        <v>0.003270223752151457</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002248201438848885</v>
+        <v>0.004619692020531962</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.006019598693420436</v>
+        <v>0.00645438898450944</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003743068391866944</v>
+        <v>0.00299739357080796</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.02311621966794379</v>
+        <v>0.009612692487167517</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.003485370051635106</v>
+        <v>0.004087779690189308</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004573028464769013</v>
+        <v>0.003924162257495534</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.006515711645101707</v>
+        <v>0.008691910499139388</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0005845323741006991</v>
+        <v>0.0003086419753085989</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004766187050359694</v>
+        <v>0.009466437177280528</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0192422307364836</v>
+        <v>0.01292580494633691</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01245503597122303</v>
+        <v>0.007492550021285682</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.003395061728395032</v>
+        <v>0.01141975308641971</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001393884892086295</v>
+        <v>0.003350970017636645</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0006613756613756405</v>
+        <v>0.002777777777777735</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001293900184842933</v>
+        <v>0.001763668430335041</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00351867940920938</v>
+        <v>0.0121198957428323</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01483812949640285</v>
+        <v>0.01451236584227717</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0007495590828923926</v>
+        <v>0.001102292768959401</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00669964028776977</v>
+        <v>0.01427904806346243</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.009239384041063925</v>
+        <v>0.009110259684972376</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001213252449836677</v>
+        <v>0.002280550774526646</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002473021582733792</v>
+        <v>0.005082536924413517</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02023381294964027</v>
+        <v>0.00673327541268458</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.009556907037358831</v>
+        <v>0.008411654135338342</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002963917525773252</v>
+        <v>0.005260791366906459</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.000695047784535241</v>
+        <v>0.0004409171075837603</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.009937050359712185</v>
+        <v>0.005065985525755679</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.01034482758620688</v>
+        <v>0.003788846317581973</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005935251798561148</v>
+        <v>0.002878006872852223</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.006768837803320526</v>
+        <v>0.001079136690647498</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.005575539568345311</v>
+        <v>0.00625</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.008429118773946332</v>
+        <v>0.01309523809523804</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001866542230517965</v>
+        <v>0.0001277139208173628</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001166588894073728</v>
+        <v>0.00111876075731494</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0007988721804511156</v>
+        <v>0.001528776978417301</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001798561151078903</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002426564495530004</v>
+        <v>0.001290877796901857</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005068728522336851</v>
+        <v>0.004091726618705027</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001159793814432986</v>
+        <v>0.001340110905730196</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0008591065292096189</v>
+        <v>0.001890034364261162</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.008679421371908535</v>
+        <v>0.003593093793747082</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.003956834532374087</v>
+        <v>0.003306878306878258</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001493233784414372</v>
+        <v>0.002957486136783794</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.004946043165467595</v>
+        <v>0.008376288659793818</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.004316546762589901</v>
+        <v>0.01030499075785587</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002448453608247458</v>
+        <v>0.006099656357388294</v>
       </c>
     </row>
   </sheetData>
